--- a/example/example-1.xlsx
+++ b/example/example-1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonh\HolyMoly\003_Work\Work\Projects\audio-vault\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157F1177-C7B2-40DD-AFE5-D947BE61E055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D979CF-B596-49C7-8703-06B91C58338F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2A71B1F5-E89A-4B34-BFAC-84675E1F45F8}"/>
   </bookViews>
@@ -33,6 +33,62 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>Song Index</t>
+  </si>
+  <si>
+    <t>Song Name</t>
+  </si>
+  <si>
+    <t>Artist Name</t>
+  </si>
+  <si>
+    <t>Song Length</t>
+  </si>
+  <si>
+    <t>You Tube Link</t>
+  </si>
+  <si>
+    <t>Spotify Link</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2KH16WveTQWT6KOG9Rg6e2?si=469702c90eb649cd</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2avaSeKHI5l4sLruVfLdi2?si=6d3403ce160d4d64</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/2GgxS8bUT5G25QJTsfSv0R?si=b3997619cd0f4cc1</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ob8TNqQw2hY</t>
+  </si>
+  <si>
+    <t>Eye of the Tiger</t>
+  </si>
+  <si>
+    <t>Survivor</t>
+  </si>
+  <si>
+    <t>Burning Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn </t>
+  </si>
+  <si>
+    <t>Ellie Goulding</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZtpTOTi2jqo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CGyEd0aKWZE</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66,8 +122,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -402,9 +459,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C7C656-39E6-45F2-B613-57E5E745B70D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.17083333333333334</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.16041666666666668</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.16041666666666668</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>